--- a/docs/public/exam/2017-shang-1.xlsx
+++ b/docs/public/exam/2017-shang-1.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="14">
   <si>
     <t>序号</t>
   </si>
@@ -1493,8 +1493,12 @@
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="G9" s="5">
+        <v>20261002</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="10" ht="15" spans="1:8">
       <c r="A10" s="6">

--- a/docs/public/exam/2017-shang-1.xlsx
+++ b/docs/public/exam/2017-shang-1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="23040" windowHeight="10455"/>
   </bookViews>
   <sheets>
     <sheet name="2016年上半年" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="17">
   <si>
     <t>序号</t>
   </si>
@@ -56,16 +56,25 @@
     <t>D</t>
   </si>
   <si>
+    <t>计算题。</t>
+  </si>
+  <si>
     <t>C</t>
   </si>
   <si>
     <t>校验码：核心公式</t>
   </si>
   <si>
-    <t>计算题。</t>
+    <t>概念题。</t>
   </si>
   <si>
-    <t>概念题。</t>
+    <t>复杂概念题。</t>
+  </si>
+  <si>
+    <t>跳过，过于复杂。</t>
+  </si>
+  <si>
+    <t>概念题，编程题。</t>
   </si>
   <si>
     <t>答题数量：</t>
@@ -730,8 +739,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
@@ -773,7 +785,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1308,1359 +1329,1396 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H79"/>
-  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9.8141592920354" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="4" max="4" width="4.45454545454545" customWidth="1"/>
-    <col min="5" max="5" width="37.2727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.18181818181818" customWidth="1"/>
-    <col min="7" max="7" width="10.2727272727273"/>
+    <col min="4" max="4" width="4.45132743362832" customWidth="1"/>
+    <col min="5" max="5" width="37.2743362831858" customWidth="1"/>
+    <col min="6" max="6" width="5.1858407079646" customWidth="1"/>
+    <col min="7" max="7" width="10.2743362831858"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:8">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="14.25" spans="1:8">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-    </row>
-    <row r="2" ht="15" spans="1:8">
-      <c r="A2" s="2">
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+    </row>
+    <row r="2" ht="14.25" spans="1:8">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="4" t="str">
+      <c r="E2" s="4"/>
+      <c r="F2" s="5" t="str">
         <f>IF(B2=D2,"真","假")</f>
         <v>真</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" ht="15" spans="1:8">
-      <c r="A3" s="2">
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+    </row>
+    <row r="3" ht="14.25" spans="1:8">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="4" t="str">
+      <c r="E3" s="4"/>
+      <c r="F3" s="5" t="str">
         <f t="shared" ref="F3:F34" si="0">IF(B3=D3,"真","假")</f>
         <v>真</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-    </row>
-    <row r="4" ht="15" spans="1:8">
-      <c r="A4" s="2">
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" ht="14.25" spans="1:8">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" ht="15" spans="1:8">
-      <c r="A5" s="6">
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" ht="14.25" spans="1:8">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="15" spans="1:8">
-      <c r="A6" s="6">
+      <c r="B5" s="7"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7" t="s">
+      <c r="E5" s="8"/>
+      <c r="F5" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>假</v>
+      </c>
+      <c r="G5" s="6">
+        <v>20261003</v>
+      </c>
+      <c r="H5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="7" t="s">
+    </row>
+    <row r="6" s="1" customFormat="1" ht="14.25" hidden="1" spans="1:8">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="8" t="str">
+      <c r="E6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="9" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="10">
         <v>20261002</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" hidden="1" spans="1:8">
+      <c r="A7" s="11">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="F7" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>假</v>
+      </c>
+      <c r="G7" s="6">
+        <v>20261002</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" spans="1:8">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" ht="14.25" hidden="1" spans="1:8">
+      <c r="A9" s="11">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="F9" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>假</v>
+      </c>
+      <c r="G9" s="6">
+        <v>20261002</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" spans="1:8">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G10" s="6">
+        <v>20261003</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" spans="1:8">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" ht="15" spans="1:8">
-      <c r="A7" s="10">
+      <c r="B11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11" t="s">
+      <c r="C11" s="4"/>
+      <c r="D11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="12" t="str">
+      <c r="E11" s="4"/>
+      <c r="F11" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+    </row>
+    <row r="12" ht="14.25" hidden="1" spans="1:8">
+      <c r="A12" s="11">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="13" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="G7" s="5">
-        <v>20261002</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="G12" s="6">
+        <v>20261003</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" ht="15" spans="1:8">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
+    <row r="13" ht="14.25" spans="1:8">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+    </row>
+    <row r="14" ht="14.25" spans="1:8">
+      <c r="A14" s="7">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" ht="14.25" spans="1:8">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" ht="14.25" spans="1:8">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" ht="14.25" spans="1:8">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" ht="14.25" spans="1:8">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+    </row>
+    <row r="19" ht="14.25" spans="1:8">
+      <c r="A19" s="7">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+    </row>
+    <row r="20" ht="14.25" spans="1:8">
+      <c r="A20" s="7">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+    </row>
+    <row r="21" ht="14.25" spans="1:8">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3" t="s">
+      <c r="C21" s="4"/>
+      <c r="D21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" ht="15" spans="1:8">
-      <c r="A9" s="10">
-        <v>8</v>
-      </c>
-      <c r="B9" s="10" t="s">
+      <c r="E21" s="4"/>
+      <c r="F21" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" ht="14.25" hidden="1" spans="1:8">
+      <c r="A22" s="11">
+        <v>21</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="12"/>
+      <c r="F22" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>假</v>
+      </c>
+      <c r="G22" s="6">
+        <v>20261003</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" spans="1:8">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+    </row>
+    <row r="24" ht="14.25" spans="1:8">
+      <c r="A24" s="7">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+    </row>
+    <row r="25" ht="14.25" spans="1:8">
+      <c r="A25" s="7">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+    </row>
+    <row r="26" ht="14.25" spans="1:8">
+      <c r="A26" s="7">
+        <v>25</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+    </row>
+    <row r="27" ht="14.25" spans="1:8">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+    </row>
+    <row r="28" ht="14.25" spans="1:8">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+    </row>
+    <row r="29" ht="14.25" spans="1:8">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="12" t="str">
+      <c r="C29" s="4"/>
+      <c r="D29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+    </row>
+    <row r="30" s="2" customFormat="1" ht="14.25" spans="1:8">
+      <c r="A30" s="15">
+        <v>29</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="16"/>
+      <c r="F30" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+    </row>
+    <row r="31" ht="14.25" spans="1:8">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+    </row>
+    <row r="32" ht="14.25" spans="1:8">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+    </row>
+    <row r="33" ht="14.25" hidden="1" spans="1:8">
+      <c r="A33" s="11">
+        <v>32</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" s="12"/>
+      <c r="F33" s="13" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="G9" s="5">
-        <v>20261002</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="G33" s="6">
+        <v>20261003</v>
+      </c>
+      <c r="H33" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="1:8">
-      <c r="A10" s="6">
+    <row r="34" ht="14.25" hidden="1" spans="1:8">
+      <c r="A34" s="11">
+        <v>33</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E34" s="12"/>
+      <c r="F34" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>假</v>
+      </c>
+      <c r="G34" s="6">
+        <v>20261003</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25" hidden="1" spans="1:8">
+      <c r="A35" s="11">
+        <v>34</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" s="12"/>
+      <c r="F35" s="13" t="str">
+        <f t="shared" ref="F35:F76" si="1">IF(B35=D35,"真","假")</f>
+        <v>假</v>
+      </c>
+      <c r="G35" s="6">
+        <v>20261003</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" spans="1:8">
+      <c r="A36" s="7">
+        <v>35</v>
+      </c>
+      <c r="B36" s="7"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+    </row>
+    <row r="37" ht="14.25" spans="1:8">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+    </row>
+    <row r="38" ht="14.25" spans="1:8">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+    </row>
+    <row r="39" ht="14.25" spans="1:8">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="4"/>
+      <c r="F39" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+    </row>
+    <row r="40" ht="14.25" spans="1:8">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+    </row>
+    <row r="41" ht="14.25" spans="1:8">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+    </row>
+    <row r="42" ht="14.25" spans="1:8">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" ht="15" spans="1:8">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="C42" s="4"/>
+      <c r="D42" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+    </row>
+    <row r="43" ht="14.25" spans="1:8">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+    </row>
+    <row r="44" ht="14.25" spans="1:8">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+    </row>
+    <row r="45" ht="14.25" hidden="1" spans="1:8">
+      <c r="A45" s="11">
+        <v>44</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" ht="15" spans="1:8">
-      <c r="A12" s="10">
-        <v>11</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="12" t="str">
-        <f t="shared" si="0"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="13" t="str">
+        <f t="shared" si="1"/>
         <v>假</v>
       </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" ht="15" spans="1:8">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-    </row>
-    <row r="14" ht="15" spans="1:8">
-      <c r="A14" s="6">
-        <v>13</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" ht="15" spans="1:8">
-      <c r="A15" s="2">
+      <c r="G45" s="6">
+        <v>20261003</v>
+      </c>
+      <c r="H45" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" ht="15" spans="1:8">
-      <c r="A16" s="2">
+    </row>
+    <row r="46" ht="14.25" spans="1:8">
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+    </row>
+    <row r="47" ht="14.25" spans="1:8">
+      <c r="A47" s="3">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+    </row>
+    <row r="48" ht="14.25" spans="1:8">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+    </row>
+    <row r="49" ht="14.25" spans="1:8">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+    </row>
+    <row r="50" ht="14.25" spans="1:8">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+    </row>
+    <row r="51" ht="14.25" spans="1:8">
+      <c r="A51" s="7">
+        <v>50</v>
+      </c>
+      <c r="B51" s="7"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+    </row>
+    <row r="52" ht="14.25" spans="1:8">
+      <c r="A52" s="7">
+        <v>51</v>
+      </c>
+      <c r="B52" s="7"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+    </row>
+    <row r="53" ht="14.25" spans="1:8">
+      <c r="A53" s="7">
+        <v>52</v>
+      </c>
+      <c r="B53" s="7"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+    </row>
+    <row r="54" ht="14.25" spans="1:8">
+      <c r="A54" s="7">
+        <v>53</v>
+      </c>
+      <c r="B54" s="7"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+    </row>
+    <row r="55" ht="14.25" spans="1:8">
+      <c r="A55" s="7">
+        <v>54</v>
+      </c>
+      <c r="B55" s="7"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+    </row>
+    <row r="56" ht="14.25" spans="1:8">
+      <c r="A56" s="7">
+        <v>55</v>
+      </c>
+      <c r="B56" s="7"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+    </row>
+    <row r="57" ht="14.25" spans="1:8">
+      <c r="A57" s="7">
+        <v>56</v>
+      </c>
+      <c r="B57" s="7"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+    </row>
+    <row r="58" ht="14.25" spans="1:8">
+      <c r="A58" s="7">
+        <v>57</v>
+      </c>
+      <c r="B58" s="7"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+    </row>
+    <row r="59" ht="14.25" spans="1:8">
+      <c r="A59" s="7">
+        <v>58</v>
+      </c>
+      <c r="B59" s="7"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+    </row>
+    <row r="60" ht="14.25" spans="1:8">
+      <c r="A60" s="7">
+        <v>59</v>
+      </c>
+      <c r="B60" s="7"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+    </row>
+    <row r="61" ht="14.25" spans="1:8">
+      <c r="A61" s="7">
+        <v>60</v>
+      </c>
+      <c r="B61" s="7"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+    </row>
+    <row r="62" ht="14.25" spans="1:8">
+      <c r="A62" s="7">
+        <v>61</v>
+      </c>
+      <c r="B62" s="7"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+    </row>
+    <row r="63" ht="14.25" spans="1:8">
+      <c r="A63" s="7">
+        <v>62</v>
+      </c>
+      <c r="B63" s="7"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+    </row>
+    <row r="64" ht="14.25" spans="1:8">
+      <c r="A64" s="7">
+        <v>63</v>
+      </c>
+      <c r="B64" s="7"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+    </row>
+    <row r="65" ht="14.25" spans="1:8">
+      <c r="A65" s="7">
+        <v>64</v>
+      </c>
+      <c r="B65" s="7"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+    </row>
+    <row r="66" ht="14.25" spans="1:8">
+      <c r="A66" s="7">
+        <v>65</v>
+      </c>
+      <c r="B66" s="7"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+    </row>
+    <row r="67" s="1" customFormat="1" ht="14.25" spans="1:8">
+      <c r="A67" s="7">
+        <v>66</v>
+      </c>
+      <c r="B67" s="7"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G67" s="10"/>
+      <c r="H67" s="10"/>
+    </row>
+    <row r="68" s="1" customFormat="1" ht="14.25" spans="1:8">
+      <c r="A68" s="7">
+        <v>67</v>
+      </c>
+      <c r="B68" s="7"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G68" s="10"/>
+      <c r="H68" s="10"/>
+    </row>
+    <row r="69" ht="14.25" spans="1:8">
+      <c r="A69" s="7">
+        <v>68</v>
+      </c>
+      <c r="B69" s="7"/>
+      <c r="C69" s="8"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+    </row>
+    <row r="70" ht="14.25" spans="1:8">
+      <c r="A70" s="7">
+        <v>69</v>
+      </c>
+      <c r="B70" s="7"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+    </row>
+    <row r="71" ht="14.25" spans="1:8">
+      <c r="A71" s="3">
+        <v>70</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E71" s="4"/>
+      <c r="F71" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+    </row>
+    <row r="72" ht="14.25" spans="1:8">
+      <c r="A72" s="7">
+        <v>71</v>
+      </c>
+      <c r="B72" s="7"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+    </row>
+    <row r="73" ht="14.25" spans="1:8">
+      <c r="A73" s="7">
+        <v>72</v>
+      </c>
+      <c r="B73" s="7"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="8"/>
+      <c r="F73" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+    </row>
+    <row r="74" ht="14.25" spans="1:8">
+      <c r="A74" s="7">
+        <v>73</v>
+      </c>
+      <c r="B74" s="7"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+    </row>
+    <row r="75" ht="14.25" spans="1:8">
+      <c r="A75" s="7">
+        <v>74</v>
+      </c>
+      <c r="B75" s="7"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
+    </row>
+    <row r="76" ht="14.25" spans="1:8">
+      <c r="A76" s="7">
+        <v>75</v>
+      </c>
+      <c r="B76" s="7"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
+    </row>
+    <row r="78" ht="13.85" spans="1:2">
+      <c r="A78" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" ht="15" spans="1:8">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" ht="15" spans="1:8">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-    </row>
-    <row r="19" ht="15" spans="1:8">
-      <c r="A19" s="6">
-        <v>18</v>
-      </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" ht="15" spans="1:8">
-      <c r="A20" s="6">
-        <v>19</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-    </row>
-    <row r="21" ht="15" spans="1:8">
-      <c r="A21" s="2">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-    </row>
-    <row r="22" ht="15" spans="1:8">
-      <c r="A22" s="10">
-        <v>21</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>假</v>
-      </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-    </row>
-    <row r="23" ht="15" spans="1:8">
-      <c r="A23" s="2">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="24" ht="15" spans="1:8">
-      <c r="A24" s="6">
-        <v>23</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" ht="15" spans="1:8">
-      <c r="A25" s="6">
-        <v>24</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-    </row>
-    <row r="26" ht="15" spans="1:8">
-      <c r="A26" s="6">
-        <v>25</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-    </row>
-    <row r="27" ht="15" spans="1:8">
-      <c r="A27" s="2">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-    </row>
-    <row r="28" ht="15" spans="1:8">
-      <c r="A28" s="2">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-    </row>
-    <row r="29" ht="15" spans="1:8">
-      <c r="A29" s="2">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-    </row>
-    <row r="30" ht="15" spans="1:8">
-      <c r="A30" s="10">
-        <v>29</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="11"/>
-      <c r="F30" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>假</v>
-      </c>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-    </row>
-    <row r="31" ht="15" spans="1:8">
-      <c r="A31" s="2">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-    </row>
-    <row r="32" ht="15" spans="1:8">
-      <c r="A32" s="2">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-    </row>
-    <row r="33" ht="15" spans="1:8">
-      <c r="A33" s="10">
-        <v>32</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E33" s="11"/>
-      <c r="F33" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>假</v>
-      </c>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-    </row>
-    <row r="34" ht="15" spans="1:8">
-      <c r="A34" s="10">
-        <v>33</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E34" s="11"/>
-      <c r="F34" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>假</v>
-      </c>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-    </row>
-    <row r="35" ht="15" spans="1:8">
-      <c r="A35" s="10">
-        <v>34</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E35" s="11"/>
-      <c r="F35" s="12" t="str">
-        <f t="shared" ref="F35:F66" si="1">IF(B35=D35,"真","假")</f>
-        <v>假</v>
-      </c>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-    </row>
-    <row r="36" ht="15" spans="1:8">
-      <c r="A36" s="6">
-        <v>35</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-    </row>
-    <row r="37" ht="15" spans="1:8">
-      <c r="A37" s="2">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E37" s="3"/>
-      <c r="F37" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-    </row>
-    <row r="38" ht="15" spans="1:8">
-      <c r="A38" s="2">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E38" s="3"/>
-      <c r="F38" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-    </row>
-    <row r="39" ht="15" spans="1:8">
-      <c r="A39" s="2">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-    </row>
-    <row r="40" ht="15" spans="1:8">
-      <c r="A40" s="2">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-    </row>
-    <row r="41" ht="15" spans="1:8">
-      <c r="A41" s="2">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-    </row>
-    <row r="42" ht="15" spans="1:8">
-      <c r="A42" s="2">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-    </row>
-    <row r="43" ht="15" spans="1:8">
-      <c r="A43" s="2">
-        <v>42</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E43" s="3"/>
-      <c r="F43" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-    </row>
-    <row r="44" ht="15" spans="1:8">
-      <c r="A44" s="2">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-    </row>
-    <row r="45" ht="15" spans="1:8">
-      <c r="A45" s="10">
-        <v>44</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E45" s="11"/>
-      <c r="F45" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>假</v>
-      </c>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-    </row>
-    <row r="46" ht="15" spans="1:8">
-      <c r="A46" s="2">
-        <v>45</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-    </row>
-    <row r="47" ht="15" spans="1:8">
-      <c r="A47" s="2">
-        <v>46</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E47" s="3"/>
-      <c r="F47" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-    </row>
-    <row r="48" ht="15" spans="1:8">
-      <c r="A48" s="2">
-        <v>47</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" s="3"/>
-      <c r="F48" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-    </row>
-    <row r="49" ht="15" spans="1:8">
-      <c r="A49" s="2">
-        <v>48</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="3"/>
-      <c r="F49" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-    </row>
-    <row r="50" ht="15" spans="1:8">
-      <c r="A50" s="2">
-        <v>49</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E50" s="3"/>
-      <c r="F50" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-    </row>
-    <row r="51" ht="15" spans="1:8">
-      <c r="A51" s="6">
-        <v>50</v>
-      </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-    </row>
-    <row r="52" ht="15" spans="1:8">
-      <c r="A52" s="6">
-        <v>51</v>
-      </c>
-      <c r="B52" s="6"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-    </row>
-    <row r="53" ht="15" spans="1:8">
-      <c r="A53" s="6">
-        <v>52</v>
-      </c>
-      <c r="B53" s="6"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
-    </row>
-    <row r="54" ht="15" spans="1:8">
-      <c r="A54" s="6">
-        <v>53</v>
-      </c>
-      <c r="B54" s="6"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
-    </row>
-    <row r="55" ht="15" spans="1:8">
-      <c r="A55" s="6">
-        <v>54</v>
-      </c>
-      <c r="B55" s="6"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
-    </row>
-    <row r="56" ht="15" spans="1:8">
-      <c r="A56" s="6">
-        <v>55</v>
-      </c>
-      <c r="B56" s="6"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
-    </row>
-    <row r="57" ht="15" spans="1:8">
-      <c r="A57" s="6">
-        <v>56</v>
-      </c>
-      <c r="B57" s="6"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-    </row>
-    <row r="58" ht="15" spans="1:8">
-      <c r="A58" s="6">
-        <v>57</v>
-      </c>
-      <c r="B58" s="6"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G58" s="5"/>
-      <c r="H58" s="5"/>
-    </row>
-    <row r="59" ht="15" spans="1:8">
-      <c r="A59" s="6">
-        <v>58</v>
-      </c>
-      <c r="B59" s="6"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
-    </row>
-    <row r="60" ht="15" spans="1:8">
-      <c r="A60" s="6">
-        <v>59</v>
-      </c>
-      <c r="B60" s="6"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
-    </row>
-    <row r="61" ht="15" spans="1:8">
-      <c r="A61" s="6">
-        <v>60</v>
-      </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-    </row>
-    <row r="62" ht="15" spans="1:8">
-      <c r="A62" s="6">
-        <v>61</v>
-      </c>
-      <c r="B62" s="6"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-    </row>
-    <row r="63" ht="15" spans="1:8">
-      <c r="A63" s="6">
-        <v>62</v>
-      </c>
-      <c r="B63" s="6"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-    </row>
-    <row r="64" ht="15" spans="1:8">
-      <c r="A64" s="6">
-        <v>63</v>
-      </c>
-      <c r="B64" s="6"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-    </row>
-    <row r="65" ht="15" spans="1:8">
-      <c r="A65" s="6">
-        <v>64</v>
-      </c>
-      <c r="B65" s="6"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-    </row>
-    <row r="66" ht="15" spans="1:8">
-      <c r="A66" s="6">
-        <v>65</v>
-      </c>
-      <c r="B66" s="6"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-    </row>
-    <row r="67" s="1" customFormat="1" ht="15" spans="1:8">
-      <c r="A67" s="6">
-        <v>66</v>
-      </c>
-      <c r="B67" s="6"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="8" t="str">
-        <f>IF(B67=D67,"真","假")</f>
-        <v>真</v>
-      </c>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
-    </row>
-    <row r="68" s="1" customFormat="1" ht="15" spans="1:8">
-      <c r="A68" s="6">
-        <v>67</v>
-      </c>
-      <c r="B68" s="6"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="8" t="str">
-        <f>IF(B68=D68,"真","假")</f>
-        <v>真</v>
-      </c>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
-    </row>
-    <row r="69" ht="15" spans="1:8">
-      <c r="A69" s="6">
-        <v>68</v>
-      </c>
-      <c r="B69" s="6"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="8" t="str">
-        <f>IF(B69=D69,"真","假")</f>
-        <v>真</v>
-      </c>
-      <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
-    </row>
-    <row r="70" ht="15" spans="1:8">
-      <c r="A70" s="6">
-        <v>69</v>
-      </c>
-      <c r="B70" s="6"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="8" t="str">
-        <f>IF(B70=D70,"真","假")</f>
-        <v>真</v>
-      </c>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
-    </row>
-    <row r="71" ht="15" spans="1:8">
-      <c r="A71" s="2">
-        <v>70</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E71" s="3"/>
-      <c r="F71" s="4" t="str">
-        <f>IF(B71=D71,"真","假")</f>
-        <v>真</v>
-      </c>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-    </row>
-    <row r="72" ht="15" spans="1:8">
-      <c r="A72" s="6">
-        <v>71</v>
-      </c>
-      <c r="B72" s="6"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="8" t="str">
-        <f>IF(B72=D72,"真","假")</f>
-        <v>真</v>
-      </c>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-    </row>
-    <row r="73" ht="15" spans="1:8">
-      <c r="A73" s="6">
-        <v>72</v>
-      </c>
-      <c r="B73" s="6"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="8" t="str">
-        <f>IF(B73=D73,"真","假")</f>
-        <v>真</v>
-      </c>
-      <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
-    </row>
-    <row r="74" ht="15" spans="1:8">
-      <c r="A74" s="6">
-        <v>73</v>
-      </c>
-      <c r="B74" s="6"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="8" t="str">
-        <f>IF(B74=D74,"真","假")</f>
-        <v>真</v>
-      </c>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-    </row>
-    <row r="75" ht="15" spans="1:8">
-      <c r="A75" s="6">
-        <v>74</v>
-      </c>
-      <c r="B75" s="6"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="8" t="str">
-        <f>IF(B75=D75,"真","假")</f>
-        <v>真</v>
-      </c>
-      <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
-    </row>
-    <row r="76" ht="15" spans="1:8">
-      <c r="A76" s="6">
-        <v>75</v>
-      </c>
-      <c r="B76" s="6"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="8" t="str">
-        <f>IF(B76=D76,"真","假")</f>
-        <v>真</v>
-      </c>
-      <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
-    </row>
-    <row r="78" ht="14.5" spans="1:2">
-      <c r="A78" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B78" s="14">
+      <c r="B78" s="6">
         <f>COUNTA(B2:B74)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="79" ht="14.5" spans="1:2">
-      <c r="A79" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B79" s="14">
+    <row r="79" ht="13.85" spans="1:2">
+      <c r="A79" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B79" s="6">
         <f>COUNTIF(F4:F76,"真")</f>
         <v>63</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H79" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="6">
+      <filters blank="1"/>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/public/exam/2017-shang-1.xlsx
+++ b/docs/public/exam/2017-shang-1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10455"/>
+    <workbookView windowWidth="21000" windowHeight="17080"/>
   </bookViews>
   <sheets>
     <sheet name="2016年上半年" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="20">
   <si>
     <t>序号</t>
   </si>
@@ -71,7 +71,16 @@
     <t>复杂概念题。</t>
   </si>
   <si>
+    <t>概念题,计算题。</t>
+  </si>
+  <si>
+    <t>概念题，计算题。</t>
+  </si>
+  <si>
     <t>跳过，过于复杂。</t>
+  </si>
+  <si>
+    <t>计算题，复杂。</t>
   </si>
   <si>
     <t>概念题，编程题。</t>
@@ -739,11 +748,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
@@ -792,9 +798,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1331,1385 +1334,1405 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:H79"/>
-  <sheetFormatPr defaultColWidth="9.8141592920354" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="4" max="4" width="4.45132743362832" customWidth="1"/>
-    <col min="5" max="5" width="37.2743362831858" customWidth="1"/>
-    <col min="6" max="6" width="5.1858407079646" customWidth="1"/>
-    <col min="7" max="7" width="10.2743362831858"/>
+    <col min="4" max="4" width="4.45454545454545" customWidth="1"/>
+    <col min="5" max="5" width="37.2727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.18181818181818" customWidth="1"/>
+    <col min="7" max="7" width="10.2727272727273"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:8">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="15" spans="1:8">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-    </row>
-    <row r="2" ht="14.25" spans="1:8">
-      <c r="A2" s="3">
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+    </row>
+    <row r="2" ht="15" spans="1:8">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5" t="str">
+      <c r="E2" s="3"/>
+      <c r="F2" s="4" t="str">
         <f>IF(B2=D2,"真","假")</f>
         <v>真</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-    </row>
-    <row r="3" ht="14.25" spans="1:8">
-      <c r="A3" s="3">
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" ht="15" spans="1:8">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="5" t="str">
+      <c r="E3" s="3"/>
+      <c r="F3" s="4" t="str">
         <f t="shared" ref="F3:F34" si="0">IF(B3=D3,"真","假")</f>
         <v>真</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-    </row>
-    <row r="4" ht="14.25" spans="1:8">
-      <c r="A4" s="3">
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" ht="15" spans="1:8">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-    </row>
-    <row r="5" ht="14.25" spans="1:8">
-      <c r="A5" s="7">
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" ht="15" spans="1:8">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="9" t="str">
+      <c r="E5" s="7"/>
+      <c r="F5" s="8" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>20261003</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="14.25" hidden="1" spans="1:8">
-      <c r="A6" s="7">
+    <row r="6" s="1" customFormat="1" ht="15" hidden="1" spans="1:8">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="9" t="str">
+      <c r="F6" s="8" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <v>20261002</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="14.25" hidden="1" spans="1:8">
-      <c r="A7" s="11">
+    <row r="7" ht="15" hidden="1" spans="1:8">
+      <c r="A7" s="10">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12" t="s">
+      <c r="C7" s="11"/>
+      <c r="D7" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="13" t="str">
+      <c r="E7" s="11"/>
+      <c r="F7" s="12" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <v>20261002</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" ht="14.25" spans="1:8">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
+    <row r="8" ht="15" spans="1:8">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4" t="s">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-    </row>
-    <row r="9" ht="14.25" hidden="1" spans="1:8">
-      <c r="A9" s="11">
+      <c r="E8" s="3"/>
+      <c r="F8" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" ht="15" hidden="1" spans="1:8">
+      <c r="A9" s="10">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="13" t="str">
+      <c r="C9" s="11"/>
+      <c r="D9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="11"/>
+      <c r="F9" s="12" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>20261002</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" ht="14.25" spans="1:8">
-      <c r="A10" s="7">
+    <row r="10" ht="15" spans="1:8">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G10" s="6">
+      <c r="B10" s="6"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G10" s="5">
         <v>20261003</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" ht="14.25" spans="1:8">
-      <c r="A11" s="3">
+    <row r="11" ht="15" spans="1:8">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4" t="s">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12" ht="14.25" hidden="1" spans="1:8">
-      <c r="A12" s="11">
+      <c r="E11" s="3"/>
+      <c r="F11" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" ht="15" hidden="1" spans="1:8">
+      <c r="A12" s="10">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="13" t="str">
+      <c r="C12" s="11"/>
+      <c r="D12" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="11"/>
+      <c r="F12" s="12" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>20261003</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="1:8">
-      <c r="A13" s="3">
+    <row r="13" ht="15" spans="1:8">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" ht="14.25" spans="1:8">
-      <c r="A14" s="7">
+      <c r="B13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" ht="15" spans="1:8">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" ht="14.25" spans="1:8">
-      <c r="A15" s="3">
+      <c r="B14" s="6"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G14" s="5">
+        <v>20261004</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" ht="15" spans="1:8">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16" ht="14.25" spans="1:8">
-      <c r="A16" s="3">
+      <c r="B15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" ht="15" spans="1:8">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4" t="s">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" ht="14.25" spans="1:8">
-      <c r="A17" s="3">
+      <c r="E16" s="3"/>
+      <c r="F16" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" ht="15" spans="1:8">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4" t="s">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" ht="14.25" spans="1:8">
-      <c r="A18" s="3">
+      <c r="E17" s="3"/>
+      <c r="F17" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" ht="15" spans="1:8">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-    </row>
-    <row r="19" ht="14.25" spans="1:8">
-      <c r="A19" s="7">
+      <c r="B18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" ht="15" spans="1:8">
+      <c r="A19" s="6">
         <v>18</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" ht="14.25" spans="1:8">
-      <c r="A20" s="7">
+      <c r="B19" s="6"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G19" s="5">
+        <v>20261004</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" ht="15" spans="1:8">
+      <c r="A20" s="6">
         <v>19</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" ht="14.25" spans="1:8">
-      <c r="A21" s="3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G20" s="5">
+        <v>20261004</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" ht="15" spans="1:8">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4" t="s">
+      <c r="C21" s="3"/>
+      <c r="D21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="22" ht="14.25" hidden="1" spans="1:8">
-      <c r="A22" s="11">
+      <c r="E21" s="3"/>
+      <c r="F21" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" ht="15" hidden="1" spans="1:8">
+      <c r="A22" s="10">
         <v>21</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="13" t="str">
+      <c r="C22" s="11"/>
+      <c r="D22" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="11"/>
+      <c r="F22" s="12" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="5">
         <v>20261003</v>
       </c>
-      <c r="H22" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" spans="1:8">
-      <c r="A23" s="3">
+      <c r="H22" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" ht="15" spans="1:8">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4" t="s">
+      <c r="C23" s="3"/>
+      <c r="D23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-    </row>
-    <row r="24" ht="14.25" spans="1:8">
-      <c r="A24" s="7">
+      <c r="E23" s="3"/>
+      <c r="F23" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" ht="15" spans="1:8">
+      <c r="A24" s="6">
         <v>23</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-    </row>
-    <row r="25" ht="14.25" spans="1:8">
-      <c r="A25" s="7">
+      <c r="B24" s="6"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G24" s="5">
+        <v>20261004</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" ht="15" spans="1:8">
+      <c r="A25" s="6">
         <v>24</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-    </row>
-    <row r="26" ht="14.25" spans="1:8">
-      <c r="A26" s="7">
+      <c r="B25" s="6"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G25" s="5">
+        <v>20261004</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" ht="15" spans="1:8">
+      <c r="A26" s="6">
         <v>25</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-    </row>
-    <row r="27" ht="14.25" spans="1:8">
-      <c r="A27" s="3">
+      <c r="B26" s="6"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" ht="15" spans="1:8">
+      <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4" t="s">
+      <c r="C27" s="3"/>
+      <c r="D27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-    </row>
-    <row r="28" ht="14.25" spans="1:8">
-      <c r="A28" s="3">
+      <c r="E27" s="3"/>
+      <c r="F27" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" ht="15" spans="1:8">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4" t="s">
+      <c r="C28" s="3"/>
+      <c r="D28" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-    </row>
-    <row r="29" ht="14.25" spans="1:8">
-      <c r="A29" s="3">
+      <c r="E28" s="3"/>
+      <c r="F28" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+    </row>
+    <row r="29" ht="15" spans="1:8">
+      <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4" t="s">
+      <c r="C29" s="3"/>
+      <c r="D29" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-    </row>
-    <row r="30" s="2" customFormat="1" ht="14.25" spans="1:8">
-      <c r="A30" s="15">
+      <c r="E29" s="3"/>
+      <c r="F29" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="15" spans="1:8">
+      <c r="A30" s="14">
         <v>29</v>
       </c>
-      <c r="B30" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="16"/>
-      <c r="F30" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-    </row>
-    <row r="31" ht="14.25" spans="1:8">
-      <c r="A31" s="3">
+      <c r="B30" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="15"/>
+      <c r="F30" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+    </row>
+    <row r="31" ht="15" spans="1:8">
+      <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-    </row>
-    <row r="32" ht="14.25" spans="1:8">
-      <c r="A32" s="3">
+      <c r="B31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+    </row>
+    <row r="32" ht="15" spans="1:8">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" s="4"/>
-      <c r="F32" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>真</v>
-      </c>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-    </row>
-    <row r="33" ht="14.25" hidden="1" spans="1:8">
-      <c r="A33" s="11">
+      <c r="B32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+    </row>
+    <row r="33" ht="15" hidden="1" spans="1:8">
+      <c r="A33" s="10">
         <v>32</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E33" s="12"/>
-      <c r="F33" s="13" t="str">
+      <c r="C33" s="11"/>
+      <c r="D33" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" s="11"/>
+      <c r="F33" s="12" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="G33" s="6">
+      <c r="G33" s="5">
         <v>20261003</v>
       </c>
-      <c r="H33" s="6" t="s">
+      <c r="H33" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="34" ht="14.25" hidden="1" spans="1:8">
-      <c r="A34" s="11">
+    <row r="34" ht="15" hidden="1" spans="1:8">
+      <c r="A34" s="10">
         <v>33</v>
       </c>
-      <c r="B34" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12" t="s">
+      <c r="B34" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E34" s="12"/>
-      <c r="F34" s="13" t="str">
+      <c r="E34" s="11"/>
+      <c r="F34" s="12" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="5">
         <v>20261003</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="H34" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="35" ht="14.25" hidden="1" spans="1:8">
-      <c r="A35" s="11">
+    <row r="35" ht="15" hidden="1" spans="1:8">
+      <c r="A35" s="10">
         <v>34</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E35" s="12"/>
-      <c r="F35" s="13" t="str">
+      <c r="C35" s="11"/>
+      <c r="D35" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" s="11"/>
+      <c r="F35" s="12" t="str">
         <f t="shared" ref="F35:F76" si="1">IF(B35=D35,"真","假")</f>
         <v>假</v>
       </c>
-      <c r="G35" s="6">
+      <c r="G35" s="5">
         <v>20261003</v>
       </c>
-      <c r="H35" s="6" t="s">
+      <c r="H35" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="36" ht="14.25" spans="1:8">
-      <c r="A36" s="7">
+    <row r="36" ht="15" spans="1:8">
+      <c r="A36" s="6">
         <v>35</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-    </row>
-    <row r="37" ht="14.25" spans="1:8">
-      <c r="A37" s="3">
+      <c r="B36" s="6"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" ht="15" spans="1:8">
+      <c r="A37" s="2">
         <v>36</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E37" s="4"/>
-      <c r="F37" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-    </row>
-    <row r="38" ht="14.25" spans="1:8">
-      <c r="A38" s="3">
+      <c r="B37" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" s="3"/>
+      <c r="F37" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+    </row>
+    <row r="38" ht="15" spans="1:8">
+      <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4" t="s">
+      <c r="C38" s="3"/>
+      <c r="D38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E38" s="4"/>
-      <c r="F38" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-    </row>
-    <row r="39" ht="14.25" spans="1:8">
-      <c r="A39" s="3">
+      <c r="E38" s="3"/>
+      <c r="F38" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+    </row>
+    <row r="39" ht="15" spans="1:8">
+      <c r="A39" s="2">
         <v>38</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E39" s="4"/>
-      <c r="F39" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-    </row>
-    <row r="40" ht="14.25" spans="1:8">
-      <c r="A40" s="3">
+      <c r="B39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="3"/>
+      <c r="F39" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+    </row>
+    <row r="40" ht="15" spans="1:8">
+      <c r="A40" s="2">
         <v>39</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" s="4"/>
-      <c r="F40" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-    </row>
-    <row r="41" ht="14.25" spans="1:8">
-      <c r="A41" s="3">
+      <c r="B40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+    </row>
+    <row r="41" ht="15" spans="1:8">
+      <c r="A41" s="2">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4" t="s">
+      <c r="C41" s="3"/>
+      <c r="D41" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E41" s="4"/>
-      <c r="F41" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-    </row>
-    <row r="42" ht="14.25" spans="1:8">
-      <c r="A42" s="3">
+      <c r="E41" s="3"/>
+      <c r="F41" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+    </row>
+    <row r="42" ht="15" spans="1:8">
+      <c r="A42" s="2">
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4" t="s">
+      <c r="C42" s="3"/>
+      <c r="D42" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E42" s="4"/>
-      <c r="F42" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-    </row>
-    <row r="43" ht="14.25" spans="1:8">
-      <c r="A43" s="3">
+      <c r="E42" s="3"/>
+      <c r="F42" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+    </row>
+    <row r="43" ht="15" spans="1:8">
+      <c r="A43" s="2">
         <v>42</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4" t="s">
+      <c r="C43" s="3"/>
+      <c r="D43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="4"/>
-      <c r="F43" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-    </row>
-    <row r="44" ht="14.25" spans="1:8">
-      <c r="A44" s="3">
+      <c r="E43" s="3"/>
+      <c r="F43" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+    </row>
+    <row r="44" ht="15" spans="1:8">
+      <c r="A44" s="2">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" s="4"/>
-      <c r="F44" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-    </row>
-    <row r="45" ht="14.25" hidden="1" spans="1:8">
-      <c r="A45" s="11">
+      <c r="B44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+    </row>
+    <row r="45" ht="15" hidden="1" spans="1:8">
+      <c r="A45" s="10">
         <v>44</v>
       </c>
-      <c r="B45" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12" t="s">
+      <c r="B45" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E45" s="12"/>
-      <c r="F45" s="13" t="str">
+      <c r="E45" s="11"/>
+      <c r="F45" s="12" t="str">
         <f t="shared" si="1"/>
         <v>假</v>
       </c>
-      <c r="G45" s="6">
+      <c r="G45" s="5">
         <v>20261003</v>
       </c>
-      <c r="H45" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" ht="14.25" spans="1:8">
-      <c r="A46" s="3">
+      <c r="H45" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" ht="15" spans="1:8">
+      <c r="A46" s="2">
         <v>45</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4" t="s">
+      <c r="C46" s="3"/>
+      <c r="D46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-    </row>
-    <row r="47" ht="14.25" spans="1:8">
-      <c r="A47" s="3">
+      <c r="E46" s="3"/>
+      <c r="F46" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+    </row>
+    <row r="47" ht="15" spans="1:8">
+      <c r="A47" s="2">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4" t="s">
+      <c r="C47" s="3"/>
+      <c r="D47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E47" s="4"/>
-      <c r="F47" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-    </row>
-    <row r="48" ht="14.25" spans="1:8">
-      <c r="A48" s="3">
+      <c r="E47" s="3"/>
+      <c r="F47" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+    </row>
+    <row r="48" ht="15" spans="1:8">
+      <c r="A48" s="2">
         <v>47</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" s="4"/>
-      <c r="F48" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-    </row>
-    <row r="49" ht="14.25" spans="1:8">
-      <c r="A49" s="3">
+      <c r="B48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="3"/>
+      <c r="F48" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+    </row>
+    <row r="49" ht="15" spans="1:8">
+      <c r="A49" s="2">
         <v>48</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4" t="s">
+      <c r="C49" s="3"/>
+      <c r="D49" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E49" s="4"/>
-      <c r="F49" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-    </row>
-    <row r="50" ht="14.25" spans="1:8">
-      <c r="A50" s="3">
+      <c r="E49" s="3"/>
+      <c r="F49" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+    </row>
+    <row r="50" ht="15" spans="1:8">
+      <c r="A50" s="2">
         <v>49</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4" t="s">
+      <c r="C50" s="3"/>
+      <c r="D50" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E50" s="4"/>
-      <c r="F50" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-    </row>
-    <row r="51" ht="14.25" spans="1:8">
-      <c r="A51" s="7">
+      <c r="E50" s="3"/>
+      <c r="F50" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+    </row>
+    <row r="51" ht="15" spans="1:8">
+      <c r="A51" s="6">
         <v>50</v>
       </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-    </row>
-    <row r="52" ht="14.25" spans="1:8">
-      <c r="A52" s="7">
+      <c r="B51" s="6"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+    </row>
+    <row r="52" ht="15" spans="1:8">
+      <c r="A52" s="6">
         <v>51</v>
       </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-    </row>
-    <row r="53" ht="14.25" spans="1:8">
-      <c r="A53" s="7">
+      <c r="B52" s="6"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+    </row>
+    <row r="53" ht="15" spans="1:8">
+      <c r="A53" s="6">
         <v>52</v>
       </c>
-      <c r="B53" s="7"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-    </row>
-    <row r="54" ht="14.25" spans="1:8">
-      <c r="A54" s="7">
+      <c r="B53" s="6"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+    </row>
+    <row r="54" ht="15" spans="1:8">
+      <c r="A54" s="6">
         <v>53</v>
       </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-    </row>
-    <row r="55" ht="14.25" spans="1:8">
-      <c r="A55" s="7">
+      <c r="B54" s="6"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+    </row>
+    <row r="55" ht="15" spans="1:8">
+      <c r="A55" s="6">
         <v>54</v>
       </c>
-      <c r="B55" s="7"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-    </row>
-    <row r="56" ht="14.25" spans="1:8">
-      <c r="A56" s="7">
+      <c r="B55" s="6"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+    </row>
+    <row r="56" ht="15" spans="1:8">
+      <c r="A56" s="6">
         <v>55</v>
       </c>
-      <c r="B56" s="7"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-    </row>
-    <row r="57" ht="14.25" spans="1:8">
-      <c r="A57" s="7">
+      <c r="B56" s="6"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+    </row>
+    <row r="57" ht="15" spans="1:8">
+      <c r="A57" s="6">
         <v>56</v>
       </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-    </row>
-    <row r="58" ht="14.25" spans="1:8">
-      <c r="A58" s="7">
+      <c r="B57" s="6"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+    </row>
+    <row r="58" ht="15" spans="1:8">
+      <c r="A58" s="6">
         <v>57</v>
       </c>
-      <c r="B58" s="7"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-    </row>
-    <row r="59" ht="14.25" spans="1:8">
-      <c r="A59" s="7">
+      <c r="B58" s="6"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+    </row>
+    <row r="59" ht="15" spans="1:8">
+      <c r="A59" s="6">
         <v>58</v>
       </c>
-      <c r="B59" s="7"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-    </row>
-    <row r="60" ht="14.25" spans="1:8">
-      <c r="A60" s="7">
+      <c r="B59" s="6"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+    </row>
+    <row r="60" ht="15" spans="1:8">
+      <c r="A60" s="6">
         <v>59</v>
       </c>
-      <c r="B60" s="7"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-    </row>
-    <row r="61" ht="14.25" spans="1:8">
-      <c r="A61" s="7">
+      <c r="B60" s="6"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+    </row>
+    <row r="61" ht="15" spans="1:8">
+      <c r="A61" s="6">
         <v>60</v>
       </c>
-      <c r="B61" s="7"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-    </row>
-    <row r="62" ht="14.25" spans="1:8">
-      <c r="A62" s="7">
+      <c r="B61" s="6"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+    </row>
+    <row r="62" ht="15" spans="1:8">
+      <c r="A62" s="6">
         <v>61</v>
       </c>
-      <c r="B62" s="7"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-    </row>
-    <row r="63" ht="14.25" spans="1:8">
-      <c r="A63" s="7">
+      <c r="B62" s="6"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+    </row>
+    <row r="63" ht="15" spans="1:8">
+      <c r="A63" s="6">
         <v>62</v>
       </c>
-      <c r="B63" s="7"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-    </row>
-    <row r="64" ht="14.25" spans="1:8">
-      <c r="A64" s="7">
+      <c r="B63" s="6"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+    </row>
+    <row r="64" ht="15" spans="1:8">
+      <c r="A64" s="6">
         <v>63</v>
       </c>
-      <c r="B64" s="7"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-    </row>
-    <row r="65" ht="14.25" spans="1:8">
-      <c r="A65" s="7">
+      <c r="B64" s="6"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+    </row>
+    <row r="65" ht="15" spans="1:8">
+      <c r="A65" s="6">
         <v>64</v>
       </c>
-      <c r="B65" s="7"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
-    </row>
-    <row r="66" ht="14.25" spans="1:8">
-      <c r="A66" s="7">
+      <c r="B65" s="6"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+    </row>
+    <row r="66" ht="15" spans="1:8">
+      <c r="A66" s="6">
         <v>65</v>
       </c>
-      <c r="B66" s="7"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-    </row>
-    <row r="67" s="1" customFormat="1" ht="14.25" spans="1:8">
-      <c r="A67" s="7">
+      <c r="B66" s="6"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+    </row>
+    <row r="67" s="1" customFormat="1" ht="15" spans="1:8">
+      <c r="A67" s="6">
         <v>66</v>
       </c>
-      <c r="B67" s="7"/>
-      <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G67" s="10"/>
-      <c r="H67" s="10"/>
-    </row>
-    <row r="68" s="1" customFormat="1" ht="14.25" spans="1:8">
-      <c r="A68" s="7">
+      <c r="B67" s="6"/>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G67" s="9"/>
+      <c r="H67" s="9"/>
+    </row>
+    <row r="68" s="1" customFormat="1" ht="15" spans="1:8">
+      <c r="A68" s="6">
         <v>67</v>
       </c>
-      <c r="B68" s="7"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G68" s="10"/>
-      <c r="H68" s="10"/>
-    </row>
-    <row r="69" ht="14.25" spans="1:8">
-      <c r="A69" s="7">
+      <c r="B68" s="6"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G68" s="9"/>
+      <c r="H68" s="9"/>
+    </row>
+    <row r="69" ht="15" spans="1:8">
+      <c r="A69" s="6">
         <v>68</v>
       </c>
-      <c r="B69" s="7"/>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
-    </row>
-    <row r="70" ht="14.25" spans="1:8">
-      <c r="A70" s="7">
+      <c r="B69" s="6"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+    </row>
+    <row r="70" ht="15" spans="1:8">
+      <c r="A70" s="6">
         <v>69</v>
       </c>
-      <c r="B70" s="7"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-    </row>
-    <row r="71" ht="14.25" spans="1:8">
-      <c r="A71" s="3">
+      <c r="B70" s="6"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+    </row>
+    <row r="71" ht="15" spans="1:8">
+      <c r="A71" s="2">
         <v>70</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E71" s="4"/>
-      <c r="F71" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-    </row>
-    <row r="72" ht="14.25" spans="1:8">
-      <c r="A72" s="7">
+      <c r="B71" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E71" s="3"/>
+      <c r="F71" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+    </row>
+    <row r="72" ht="15" spans="1:8">
+      <c r="A72" s="6">
         <v>71</v>
       </c>
-      <c r="B72" s="7"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-    </row>
-    <row r="73" ht="14.25" spans="1:8">
-      <c r="A73" s="7">
+      <c r="B72" s="6"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+    </row>
+    <row r="73" ht="15" spans="1:8">
+      <c r="A73" s="6">
         <v>72</v>
       </c>
-      <c r="B73" s="7"/>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G73" s="6"/>
-      <c r="H73" s="6"/>
-    </row>
-    <row r="74" ht="14.25" spans="1:8">
-      <c r="A74" s="7">
+      <c r="B73" s="6"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+    </row>
+    <row r="74" ht="15" spans="1:8">
+      <c r="A74" s="6">
         <v>73</v>
       </c>
-      <c r="B74" s="7"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-    </row>
-    <row r="75" ht="14.25" spans="1:8">
-      <c r="A75" s="7">
+      <c r="B74" s="6"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+    </row>
+    <row r="75" ht="15" spans="1:8">
+      <c r="A75" s="6">
         <v>74</v>
       </c>
-      <c r="B75" s="7"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G75" s="6"/>
-      <c r="H75" s="6"/>
-    </row>
-    <row r="76" ht="14.25" spans="1:8">
-      <c r="A76" s="7">
+      <c r="B75" s="6"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+    </row>
+    <row r="76" ht="15" spans="1:8">
+      <c r="A76" s="6">
         <v>75</v>
       </c>
-      <c r="B76" s="7"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G76" s="6"/>
-      <c r="H76" s="6"/>
-    </row>
-    <row r="78" ht="13.85" spans="1:2">
-      <c r="A78" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" s="6">
+      <c r="B76" s="6"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>真</v>
+      </c>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+    </row>
+    <row r="78" ht="14.5" spans="1:2">
+      <c r="A78" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B78" s="5">
         <f>COUNTA(B2:B74)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="79" ht="13.85" spans="1:2">
-      <c r="A79" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B79" s="6">
+    <row r="79" ht="14.5" spans="1:2">
+      <c r="A79" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B79" s="5">
         <f>COUNTIF(F4:F76,"真")</f>
         <v>63</v>
       </c>

--- a/docs/public/exam/2017-shang-1.xlsx
+++ b/docs/public/exam/2017-shang-1.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="20">
   <si>
     <t>序号</t>
   </si>
@@ -1364,7 +1364,7 @@
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
     </row>
-    <row r="2" ht="15" spans="1:8">
+    <row r="2" ht="15" hidden="1" spans="1:8">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1383,7 +1383,7 @@
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" ht="15" spans="1:8">
+    <row r="3" ht="15" hidden="1" spans="1:8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1402,7 +1402,7 @@
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" ht="15" spans="1:8">
+    <row r="4" ht="15" hidden="1" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1421,7 +1421,7 @@
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
     </row>
-    <row r="5" ht="15" spans="1:8">
+    <row r="5" ht="15" hidden="1" spans="1:8">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" ht="15" spans="1:8">
+    <row r="8" ht="15" hidden="1" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1530,7 +1530,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="1:8">
+    <row r="10" ht="15" hidden="1" spans="1:8">
       <c r="A10" s="6">
         <v>9</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="1:8">
+    <row r="11" ht="15" hidden="1" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" ht="15" spans="1:8">
+    <row r="13" ht="15" hidden="1" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1610,7 +1610,7 @@
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
     </row>
-    <row r="14" ht="15" spans="1:8">
+    <row r="14" ht="15" hidden="1" spans="1:8">
       <c r="A14" s="6">
         <v>13</v>
       </c>
@@ -1629,7 +1629,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" ht="15" spans="1:8">
+    <row r="15" ht="15" hidden="1" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1648,7 +1648,7 @@
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
     </row>
-    <row r="16" ht="15" spans="1:8">
+    <row r="16" ht="15" hidden="1" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1667,7 +1667,7 @@
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
     </row>
-    <row r="17" ht="15" spans="1:8">
+    <row r="17" ht="15" hidden="1" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1686,7 +1686,7 @@
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" ht="15" spans="1:8">
+    <row r="18" ht="15" hidden="1" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1705,7 +1705,7 @@
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
     </row>
-    <row r="19" ht="15" spans="1:8">
+    <row r="19" ht="15" hidden="1" spans="1:8">
       <c r="A19" s="6">
         <v>18</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" ht="15" spans="1:8">
+    <row r="20" ht="15" hidden="1" spans="1:8">
       <c r="A20" s="6">
         <v>19</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" ht="15" spans="1:8">
+    <row r="21" ht="15" hidden="1" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" ht="15" spans="1:8">
+    <row r="23" ht="15" hidden="1" spans="1:8">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1804,7 +1804,7 @@
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
     </row>
-    <row r="24" ht="15" spans="1:8">
+    <row r="24" ht="15" hidden="1" spans="1:8">
       <c r="A24" s="6">
         <v>23</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" ht="15" spans="1:8">
+    <row r="25" ht="15" hidden="1" spans="1:8">
       <c r="A25" s="6">
         <v>24</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" ht="15" spans="1:8">
+    <row r="26" ht="15" hidden="1" spans="1:8">
       <c r="A26" s="6">
         <v>25</v>
       </c>
@@ -1854,10 +1854,14 @@
         <f t="shared" si="0"/>
         <v>真</v>
       </c>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-    </row>
-    <row r="27" ht="15" spans="1:8">
+      <c r="G26" s="5">
+        <v>20261005</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" ht="15" hidden="1" spans="1:8">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1876,7 +1880,7 @@
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" ht="15" spans="1:8">
+    <row r="28" ht="15" hidden="1" spans="1:8">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1895,7 +1899,7 @@
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
     </row>
-    <row r="29" ht="15" spans="1:8">
+    <row r="29" ht="15" hidden="1" spans="1:8">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1914,7 +1918,7 @@
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
     </row>
-    <row r="30" s="1" customFormat="1" ht="15" spans="1:8">
+    <row r="30" s="1" customFormat="1" ht="15" hidden="1" spans="1:8">
       <c r="A30" s="14">
         <v>29</v>
       </c>
@@ -1933,7 +1937,7 @@
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" ht="15" spans="1:8">
+    <row r="31" ht="15" hidden="1" spans="1:8">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1952,7 +1956,7 @@
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
     </row>
-    <row r="32" ht="15" spans="1:8">
+    <row r="32" ht="15" hidden="1" spans="1:8">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2040,7 +2044,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" ht="15" spans="1:8">
+    <row r="36" ht="15" hidden="1" spans="1:8">
       <c r="A36" s="6">
         <v>35</v>
       </c>
@@ -2052,10 +2056,14 @@
         <f t="shared" si="1"/>
         <v>真</v>
       </c>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-    </row>
-    <row r="37" ht="15" spans="1:8">
+      <c r="G36" s="5">
+        <v>20261005</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" ht="15" hidden="1" spans="1:8">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2074,7 +2082,7 @@
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
     </row>
-    <row r="38" ht="15" spans="1:8">
+    <row r="38" ht="15" hidden="1" spans="1:8">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2093,7 +2101,7 @@
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
     </row>
-    <row r="39" ht="15" spans="1:8">
+    <row r="39" ht="15" hidden="1" spans="1:8">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2112,7 +2120,7 @@
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
     </row>
-    <row r="40" ht="15" spans="1:8">
+    <row r="40" ht="15" hidden="1" spans="1:8">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2131,7 +2139,7 @@
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
     </row>
-    <row r="41" ht="15" spans="1:8">
+    <row r="41" ht="15" hidden="1" spans="1:8">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -2150,7 +2158,7 @@
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
     </row>
-    <row r="42" ht="15" spans="1:8">
+    <row r="42" ht="15" hidden="1" spans="1:8">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2169,7 +2177,7 @@
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
     </row>
-    <row r="43" ht="15" spans="1:8">
+    <row r="43" ht="15" hidden="1" spans="1:8">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2188,7 +2196,7 @@
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
     </row>
-    <row r="44" ht="15" spans="1:8">
+    <row r="44" ht="15" hidden="1" spans="1:8">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -2230,7 +2238,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" ht="15" spans="1:8">
+    <row r="46" ht="15" hidden="1" spans="1:8">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2249,7 +2257,7 @@
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
     </row>
-    <row r="47" ht="15" spans="1:8">
+    <row r="47" ht="15" hidden="1" spans="1:8">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2268,7 +2276,7 @@
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
     </row>
-    <row r="48" ht="15" spans="1:8">
+    <row r="48" ht="15" hidden="1" spans="1:8">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -2287,7 +2295,7 @@
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
     </row>
-    <row r="49" ht="15" spans="1:8">
+    <row r="49" ht="15" hidden="1" spans="1:8">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2306,7 +2314,7 @@
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
     </row>
-    <row r="50" ht="15" spans="1:8">
+    <row r="50" ht="15" hidden="1" spans="1:8">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2325,28 +2333,38 @@
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
     </row>
-    <row r="51" ht="15" spans="1:8">
+    <row r="51" ht="15" hidden="1" spans="1:8">
       <c r="A51" s="6">
         <v>50</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
+      <c r="D51" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="E51" s="7"/>
       <c r="F51" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>真</v>
-      </c>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-    </row>
-    <row r="52" ht="15" spans="1:8">
+        <v>假</v>
+      </c>
+      <c r="G51" s="5">
+        <v>20261005</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" ht="15" hidden="1" spans="1:8">
       <c r="A52" s="6">
         <v>51</v>
       </c>
-      <c r="B52" s="6"/>
+      <c r="B52" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
+      <c r="D52" s="7" t="s">
+        <v>7</v>
+      </c>
       <c r="E52" s="7"/>
       <c r="F52" s="8" t="str">
         <f t="shared" si="1"/>
@@ -2355,13 +2373,17 @@
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
     </row>
-    <row r="53" ht="15" spans="1:8">
+    <row r="53" ht="15" hidden="1" spans="1:8">
       <c r="A53" s="6">
         <v>52</v>
       </c>
-      <c r="B53" s="6"/>
+      <c r="B53" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
+      <c r="D53" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="E53" s="7"/>
       <c r="F53" s="8" t="str">
         <f t="shared" si="1"/>
@@ -2625,7 +2647,7 @@
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
     </row>
-    <row r="71" ht="15" spans="1:8">
+    <row r="71" ht="15" hidden="1" spans="1:8">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -2719,26 +2741,35 @@
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
     </row>
-    <row r="78" ht="14.5" spans="1:2">
+    <row r="77" hidden="1"/>
+    <row r="78" ht="14.5" hidden="1" spans="1:2">
       <c r="A78" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B78" s="5">
         <f>COUNTA(B2:B74)</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="79" ht="14.5" spans="1:2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="79" ht="14.5" hidden="1" spans="1:2">
       <c r="A79" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B79" s="5">
         <f>COUNTIF(F4:F76,"真")</f>
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H79" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="3">
+      <filters blank="1"/>
+    </filterColumn>
+    <filterColumn colId="5">
+      <filters>
+        <filter val="真"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="6">
       <filters blank="1"/>
     </filterColumn>
